--- a/청첩장/시트_붙여넣기용.xlsx
+++ b/청첩장/시트_붙여넣기용.xlsx
@@ -881,16 +881,6 @@
           <t>한 장면, 한 약속, 하나의 시작.</t>
         </is>
       </c>
-      <c r="Q4" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="R4" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
       <c r="W4" t="inlineStr">
         <is>
           <t>gtrddrt7706@gmail.com</t>
